--- a/Reading&Movie/Felix Du的图书馆索引.xlsx
+++ b/Reading&Movie/Felix Du的图书馆索引.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Reading&amp;Movie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAC3FA4-C702-4ED7-9ECC-F73BF368459B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA15FB15-492C-4F84-BF1B-A8F91ACBFEB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="107">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -90,15 +90,367 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>历史</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>《芳华》</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>严歌苓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人民文学出版社,2017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小说</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>历史/文学/爱情/青春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《情书》（30周年纪念版）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩井俊二</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台湾新经典图文传播有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青春/爱情/文学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《我与地坛》（纪念版）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>史铁生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人民文学出版社,2011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亲情/爱情/哲学/文学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>历史/社会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《两个父亲》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>袁琼琼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四川文艺出版社（2016.3）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随笔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亲情/文学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《大雪将至》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗伯特.泽塔勒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南海出版公司（2018.6）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长篇小说</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《海子的诗》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江西人民出版社（2017.9）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诗歌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诗集/亲情/爱情/哲学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《品茶说天下》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《南风窗》杂志社编</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>花城出版社（2003.7）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杂文/作品集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《在细雨中呼喊》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作家出版社（2012.9）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文学/社会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《犀牛字典》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杨昌溢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重庆出版社（2015.5）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《兄弟》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《许三观卖血记》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文学/亲情/社会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《活着》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文学/社会/历史/哲学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《容忍与自由》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡适</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国华侨出版社（2021.3）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>演讲稿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《生活明朗 万物可爱》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>季羡林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏凤凰文艺出版社（2019.10）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《美学散步》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宗白华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上海人民出版社</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>美学文集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《中国文脉》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余秋雨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长江文艺出版社（2017.5）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《我从未如此眷恋人间》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>史铁生 汪曾祺等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>读者出版社（2022.2）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《被讨厌的勇气》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岸见一郎 古贺史健</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>机械工业出版社（2015.3）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哲学通俗读物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《太阳下山有月光》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林清玄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国致公出版社，2023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《看见》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柴静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广西师范大学出版社（2013.1）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>社会/文学/亲情/爱情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《Wuthering Heights》（呼啸山庄）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾米莉.勃朗特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二十一世纪出版社集团（2017.6）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《幸福的勇气》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《理想国》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柏拉图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>民主与建设出版社（2017.11）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>古希腊罗马哲学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《共产党宣言》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马克思 恩格斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英语读物/长篇小说</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马列著作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>个人收藏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人民出版社（2018.3）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《刻意学习》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scalers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北京联合出版公司（2017.6）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学习-研究</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -129,15 +481,27 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -145,19 +509,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -440,217 +822,846 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G52"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="2" max="2" width="32.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21" style="1" customWidth="1"/>
+    <col min="4" max="4" width="33.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
+      <c r="G2" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+      <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
+      <c r="B7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
+      <c r="B8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
+      <c r="B9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
+      <c r="B10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
+      <c r="B11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
+      <c r="B12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
+      <c r="B13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
+      <c r="B14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
+      <c r="B15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
+      <c r="B16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
+      <c r="B17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
+      <c r="B18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
+      <c r="B19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
+      <c r="B20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
+      <c r="B21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
+      <c r="B22" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
+      <c r="B23" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
+      <c r="B24" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
+      <c r="B25" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
+      <c r="B26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
         <v>25</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
+      <c r="B27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
         <v>26</v>
       </c>
+      <c r="B28" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>29</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>33</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>34</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>35</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>45</v>
+      </c>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
+        <v>47</v>
+      </c>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>48</v>
+      </c>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
+        <v>49</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>50</v>
+      </c>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Reading&Movie/Felix Du的图书馆索引.xlsx
+++ b/Reading&Movie/Felix Du的图书馆索引.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Reading&amp;Movie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA15FB15-492C-4F84-BF1B-A8F91ACBFEB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419EA252-6962-4654-B61C-2C1057D06D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="110">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -451,6 +451,18 @@
   </si>
   <si>
     <t>学习-研究</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《瓦尔登湖》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梭罗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>百花洲文艺出版社（2018，1）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -823,19 +835,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="21" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="33.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.375" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -846,7 +858,7 @@
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -869,7 +881,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -890,7 +902,7 @@
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -911,7 +923,7 @@
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -932,7 +944,7 @@
       </c>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -953,7 +965,7 @@
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -974,7 +986,7 @@
       </c>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -995,7 +1007,7 @@
       </c>
       <c r="G8" s="3"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1014,7 +1026,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1035,7 +1047,7 @@
       </c>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1054,7 +1066,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1075,7 +1087,7 @@
       </c>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1094,7 +1106,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1113,7 +1125,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1134,7 +1146,7 @@
       </c>
       <c r="G15" s="3"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1155,7 +1167,7 @@
       </c>
       <c r="G16" s="3"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1174,7 +1186,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1193,7 +1205,7 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -1212,7 +1224,7 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -1231,7 +1243,7 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -1250,7 +1262,7 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -1269,7 +1281,7 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -1288,7 +1300,7 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -1309,7 +1321,7 @@
       </c>
       <c r="G24" s="3"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -1328,7 +1340,7 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -1347,7 +1359,7 @@
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -1366,7 +1378,7 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -1387,7 +1399,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -1406,18 +1418,26 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+      <c r="B30" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -1428,7 +1448,7 @@
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>30</v>
       </c>
@@ -1439,7 +1459,7 @@
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -1450,7 +1470,7 @@
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>32</v>
       </c>
@@ -1461,7 +1481,7 @@
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>33</v>
       </c>
@@ -1472,7 +1492,7 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>34</v>
       </c>
@@ -1483,7 +1503,7 @@
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>35</v>
       </c>
@@ -1494,7 +1514,7 @@
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>36</v>
       </c>
@@ -1505,7 +1525,7 @@
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>37</v>
       </c>
@@ -1516,7 +1536,7 @@
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>38</v>
       </c>
@@ -1527,7 +1547,7 @@
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>39</v>
       </c>
@@ -1538,7 +1558,7 @@
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>40</v>
       </c>
@@ -1549,7 +1569,7 @@
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>41</v>
       </c>
@@ -1560,7 +1580,7 @@
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>42</v>
       </c>
@@ -1571,7 +1591,7 @@
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>43</v>
       </c>
@@ -1582,7 +1602,7 @@
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>44</v>
       </c>
@@ -1593,7 +1613,7 @@
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>45</v>
       </c>
@@ -1604,7 +1624,7 @@
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>46</v>
       </c>
@@ -1615,7 +1635,7 @@
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>47</v>
       </c>
@@ -1626,7 +1646,7 @@
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>48</v>
       </c>
@@ -1637,7 +1657,7 @@
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>49</v>
       </c>
@@ -1648,7 +1668,7 @@
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>50</v>
       </c>

--- a/Reading&Movie/Felix Du的图书馆索引.xlsx
+++ b/Reading&Movie/Felix Du的图书馆索引.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Reading&amp;Movie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419EA252-6962-4654-B61C-2C1057D06D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987F7D98-04B8-486A-AC88-50854D541348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="119">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -463,6 +463,42 @@
   </si>
   <si>
     <t>百花洲文艺出版社（2018，1）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《地下室手记》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陀思妥耶夫斯基</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四川大学出版社（2024.9）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《死屋手记》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长篇纪实小说</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《地粮·新粮》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安德烈·纪德</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广西师范大学出版社（2024.7）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>散文集-诗集</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -835,19 +871,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" style="1" customWidth="1"/>
     <col min="3" max="3" width="21" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="33.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -858,7 +894,7 @@
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -881,7 +917,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -902,7 +938,7 @@
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -923,7 +959,7 @@
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -944,7 +980,7 @@
       </c>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -965,7 +1001,7 @@
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -986,7 +1022,7 @@
       </c>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1007,7 +1043,7 @@
       </c>
       <c r="G8" s="3"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1026,7 +1062,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1047,7 +1083,7 @@
       </c>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1066,7 +1102,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1087,7 +1123,7 @@
       </c>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1106,7 +1142,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1125,7 +1161,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1146,7 +1182,7 @@
       </c>
       <c r="G15" s="3"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1167,7 +1203,7 @@
       </c>
       <c r="G16" s="3"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1186,7 +1222,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1205,7 +1241,7 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -1224,7 +1260,7 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -1243,7 +1279,7 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -1262,7 +1298,7 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -1281,7 +1317,7 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -1300,7 +1336,7 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -1321,7 +1357,7 @@
       </c>
       <c r="G24" s="3"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -1340,7 +1376,7 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -1359,7 +1395,7 @@
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -1378,7 +1414,7 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -1399,7 +1435,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -1418,7 +1454,7 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -1437,40 +1473,64 @@
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="B31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
+      <c r="B32" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>31</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
+      <c r="B33" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>32</v>
       </c>
@@ -1481,7 +1541,7 @@
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>33</v>
       </c>
@@ -1492,7 +1552,7 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>34</v>
       </c>
@@ -1503,7 +1563,7 @@
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>35</v>
       </c>
@@ -1514,7 +1574,7 @@
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>36</v>
       </c>
@@ -1525,7 +1585,7 @@
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>37</v>
       </c>
@@ -1536,7 +1596,7 @@
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>38</v>
       </c>
@@ -1547,7 +1607,7 @@
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>39</v>
       </c>
@@ -1558,7 +1618,7 @@
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>40</v>
       </c>
@@ -1569,7 +1629,7 @@
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>41</v>
       </c>
@@ -1580,7 +1640,7 @@
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>42</v>
       </c>
@@ -1591,7 +1651,7 @@
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>43</v>
       </c>
@@ -1602,7 +1662,7 @@
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>44</v>
       </c>
@@ -1613,7 +1673,7 @@
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>45</v>
       </c>
@@ -1624,7 +1684,7 @@
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>46</v>
       </c>
@@ -1635,7 +1695,7 @@
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>47</v>
       </c>
@@ -1646,7 +1706,7 @@
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>48</v>
       </c>
@@ -1657,7 +1717,7 @@
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>49</v>
       </c>
@@ -1668,7 +1728,7 @@
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>50</v>
       </c>

--- a/Reading&Movie/Felix Du的图书馆索引.xlsx
+++ b/Reading&Movie/Felix Du的图书馆索引.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Reading&amp;Movie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987F7D98-04B8-486A-AC88-50854D541348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E634EE-773F-4F69-AEC9-5AB9E1D0B7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="130">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -499,6 +499,50 @@
   </si>
   <si>
     <t>散文集-诗集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《三体》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘慈欣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重庆出版社（2008.1）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>科幻小说</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《我与地坛》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北京出版社（2020.1）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>科幻/文学/历史</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名言</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虫子从来没有被击败过</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我已不在地坛、地坛在我</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《三体：黑暗森林》</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -870,20 +914,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="21" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="33.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.125" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -893,8 +937,9 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -914,10 +959,13 @@
         <v>3</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -937,8 +985,9 @@
         <v>11</v>
       </c>
       <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -958,8 +1007,9 @@
         <v>29</v>
       </c>
       <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -979,8 +1029,9 @@
         <v>20</v>
       </c>
       <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1000,8 +1051,9 @@
         <v>24</v>
       </c>
       <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1021,8 +1073,11 @@
         <v>28</v>
       </c>
       <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1042,8 +1097,9 @@
         <v>34</v>
       </c>
       <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1061,8 +1117,9 @@
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1082,8 +1139,9 @@
         <v>43</v>
       </c>
       <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1101,8 +1159,9 @@
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1122,8 +1181,9 @@
         <v>51</v>
       </c>
       <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1141,8 +1201,9 @@
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1160,8 +1221,9 @@
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1181,8 +1243,9 @@
         <v>57</v>
       </c>
       <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1202,8 +1265,9 @@
         <v>59</v>
       </c>
       <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1221,8 +1285,9 @@
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1240,8 +1305,9 @@
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -1259,8 +1325,9 @@
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -1278,8 +1345,9 @@
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -1297,8 +1365,9 @@
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -1316,8 +1385,9 @@
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -1335,8 +1405,9 @@
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -1356,8 +1427,9 @@
         <v>87</v>
       </c>
       <c r="G24" s="3"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -1375,8 +1447,9 @@
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -1394,8 +1467,9 @@
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -1413,8 +1487,9 @@
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -1431,11 +1506,12 @@
         <v>99</v>
       </c>
       <c r="F28" s="3"/>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="3"/>
+      <c r="H28" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -1453,8 +1529,9 @@
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -1472,8 +1549,9 @@
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H30" s="3"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -1491,8 +1569,9 @@
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>30</v>
       </c>
@@ -1510,8 +1589,9 @@
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -1529,41 +1609,79 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>32</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>33</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>34</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
+      <c r="B36" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>35</v>
       </c>
@@ -1573,8 +1691,9 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>36</v>
       </c>
@@ -1584,8 +1703,9 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>37</v>
       </c>
@@ -1595,8 +1715,9 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>38</v>
       </c>
@@ -1606,8 +1727,9 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>39</v>
       </c>
@@ -1617,8 +1739,9 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>40</v>
       </c>
@@ -1628,8 +1751,9 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>41</v>
       </c>
@@ -1639,8 +1763,9 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>42</v>
       </c>
@@ -1650,8 +1775,9 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>43</v>
       </c>
@@ -1661,8 +1787,9 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H45" s="3"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>44</v>
       </c>
@@ -1672,8 +1799,9 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H46" s="3"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>45</v>
       </c>
@@ -1683,8 +1811,9 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>46</v>
       </c>
@@ -1694,8 +1823,9 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>47</v>
       </c>
@@ -1705,8 +1835,9 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>48</v>
       </c>
@@ -1716,8 +1847,9 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H50" s="3"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>49</v>
       </c>
@@ -1727,8 +1859,9 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>50</v>
       </c>
@@ -1738,10 +1871,11 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Reading&Movie/Felix Du的图书馆索引.xlsx
+++ b/Reading&Movie/Felix Du的图书馆索引.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Reading&amp;Movie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E634EE-773F-4F69-AEC9-5AB9E1D0B7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68C502B-1FB3-46AE-9853-587CEEF4DADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="133">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -543,6 +543,18 @@
   </si>
   <si>
     <t>《三体：黑暗森林》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>科幻/哲学/文学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑暗森林法则、猜疑链、技术爆炸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>限量海外代购</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -915,19 +927,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" style="1" customWidth="1"/>
     <col min="3" max="3" width="21" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="33.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="41.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -939,7 +952,7 @@
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -965,7 +978,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -987,7 +1000,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1009,7 +1022,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1031,7 +1044,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1051,9 +1064,11 @@
         <v>24</v>
       </c>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1077,7 +1092,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1099,7 +1114,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1119,7 +1134,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1141,7 +1156,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1161,7 +1176,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1183,7 +1198,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1203,7 +1218,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1223,7 +1238,7 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1245,7 +1260,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1267,7 +1282,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1287,7 +1302,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1307,7 +1322,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -1327,7 +1342,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -1347,7 +1362,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -1367,7 +1382,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -1387,7 +1402,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -1407,7 +1422,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -1429,7 +1444,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -1449,7 +1464,7 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -1469,7 +1484,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -1489,7 +1504,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -1511,7 +1526,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -1531,7 +1546,7 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -1551,7 +1566,7 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -1571,7 +1586,7 @@
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>30</v>
       </c>
@@ -1591,7 +1606,7 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -1611,7 +1626,7 @@
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>32</v>
       </c>
@@ -1635,7 +1650,7 @@
       </c>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>33</v>
       </c>
@@ -1661,7 +1676,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>34</v>
       </c>
@@ -1677,11 +1692,15 @@
       <c r="E36" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
+      <c r="F36" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="H36" s="3"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>35</v>
       </c>
@@ -1693,7 +1712,7 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>36</v>
       </c>
@@ -1705,7 +1724,7 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>37</v>
       </c>
@@ -1717,7 +1736,7 @@
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>38</v>
       </c>
@@ -1729,7 +1748,7 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>39</v>
       </c>
@@ -1741,7 +1760,7 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>40</v>
       </c>
@@ -1753,7 +1772,7 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>41</v>
       </c>
@@ -1765,7 +1784,7 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>42</v>
       </c>
@@ -1777,7 +1796,7 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>43</v>
       </c>
@@ -1789,7 +1808,7 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>44</v>
       </c>
@@ -1801,7 +1820,7 @@
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>45</v>
       </c>
@@ -1813,7 +1832,7 @@
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>46</v>
       </c>
@@ -1825,7 +1844,7 @@
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>47</v>
       </c>
@@ -1837,7 +1856,7 @@
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>48</v>
       </c>
@@ -1849,7 +1868,7 @@
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>49</v>
       </c>
@@ -1861,7 +1880,7 @@
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>50</v>
       </c>

--- a/Reading&Movie/Felix Du的图书馆索引.xlsx
+++ b/Reading&Movie/Felix Du的图书馆索引.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Reading&amp;Movie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68C502B-1FB3-46AE-9853-587CEEF4DADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B5EE88-D97F-4CA1-A9D1-E87317585D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="146">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -555,6 +555,58 @@
   </si>
   <si>
     <t>限量海外代购</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《月亮与六便士》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《三国演义》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《红楼梦》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《水浒传》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《西游记》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《悉达多》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《雪国》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赫尔曼.黑塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台海出版社（2025.3）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受赠于叶舒瑶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受赠于刘雨轩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《做自己的心理医生》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杜赢</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1442,7 +1494,9 @@
         <v>87</v>
       </c>
       <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="H24" s="3" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
@@ -1704,19 +1758,25 @@
       <c r="A37" s="3">
         <v>35</v>
       </c>
-      <c r="B37" s="3"/>
+      <c r="B37" s="3" t="s">
+        <v>133</v>
+      </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
+      <c r="H37" s="3" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>36</v>
       </c>
-      <c r="B38" s="3"/>
+      <c r="B38" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -1728,7 +1788,9 @@
       <c r="A39" s="3">
         <v>37</v>
       </c>
-      <c r="B39" s="3"/>
+      <c r="B39" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -1740,7 +1802,9 @@
       <c r="A40" s="3">
         <v>38</v>
       </c>
-      <c r="B40" s="3"/>
+      <c r="B40" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -1752,7 +1816,9 @@
       <c r="A41" s="3">
         <v>39</v>
       </c>
-      <c r="B41" s="3"/>
+      <c r="B41" s="3" t="s">
+        <v>137</v>
+      </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -1764,10 +1830,18 @@
       <c r="A42" s="3">
         <v>40</v>
       </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
+      <c r="B42" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
@@ -1776,7 +1850,9 @@
       <c r="A43" s="3">
         <v>41</v>
       </c>
-      <c r="B43" s="3"/>
+      <c r="B43" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -1788,8 +1864,12 @@
       <c r="A44" s="3">
         <v>42</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
+      <c r="B44" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>

--- a/Reading&Movie/Felix Du的图书馆索引.xlsx
+++ b/Reading&Movie/Felix Du的图书馆索引.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Reading&amp;Movie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B5EE88-D97F-4CA1-A9D1-E87317585D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923FD97B-9852-46C3-BE89-B17154CF6403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="157">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -607,6 +607,50 @@
   </si>
   <si>
     <t>杜赢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>曹雪芹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岳麓书社（2024.10）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四大名著</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴承恩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施耐庵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗贯中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《品中国文人1》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《品中国文人2》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《品中国文人3》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《品中国文人4》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《品中国文人：圣贤传》</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1777,9 +1821,15 @@
       <c r="B38" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
+      <c r="C38" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
@@ -1791,9 +1841,15 @@
       <c r="B39" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
+      <c r="C39" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
@@ -1805,9 +1861,15 @@
       <c r="B40" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
+      <c r="C40" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -1819,9 +1881,15 @@
       <c r="B41" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
+      <c r="C41" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
@@ -1880,7 +1948,9 @@
       <c r="A45" s="3">
         <v>43</v>
       </c>
-      <c r="B45" s="3"/>
+      <c r="B45" s="3" t="s">
+        <v>152</v>
+      </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -1892,7 +1962,9 @@
       <c r="A46" s="3">
         <v>44</v>
       </c>
-      <c r="B46" s="3"/>
+      <c r="B46" s="3" t="s">
+        <v>153</v>
+      </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -1904,7 +1976,9 @@
       <c r="A47" s="3">
         <v>45</v>
       </c>
-      <c r="B47" s="3"/>
+      <c r="B47" s="3" t="s">
+        <v>154</v>
+      </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -1916,7 +1990,9 @@
       <c r="A48" s="3">
         <v>46</v>
       </c>
-      <c r="B48" s="3"/>
+      <c r="B48" s="3" t="s">
+        <v>155</v>
+      </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -1928,7 +2004,9 @@
       <c r="A49" s="3">
         <v>47</v>
       </c>
-      <c r="B49" s="3"/>
+      <c r="B49" s="3" t="s">
+        <v>156</v>
+      </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>

--- a/Reading&Movie/Felix Du的图书馆索引.xlsx
+++ b/Reading&Movie/Felix Du的图书馆索引.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Reading&amp;Movie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923FD97B-9852-46C3-BE89-B17154CF6403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E631E8-CDBD-4689-B75E-F1A053985E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="161">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -651,6 +651,21 @@
   </si>
   <si>
     <t>《品中国文人：圣贤传》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘小川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上海文艺出版社（2008.5）</t>
+  </si>
+  <si>
+    <t>上海文艺出版社（2008.5）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人物研究</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1023,20 +1038,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="21" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="41.109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="33.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="41.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -1048,7 +1063,7 @@
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1074,7 +1089,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1096,7 +1111,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1118,7 +1133,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1140,7 +1155,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1164,7 +1179,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1188,7 +1203,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1210,7 +1225,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1230,7 +1245,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1252,7 +1267,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1272,7 +1287,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1294,7 +1309,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1314,7 +1329,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1334,7 +1349,7 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1356,7 +1371,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1378,7 +1393,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1398,7 +1413,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1418,7 +1433,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -1438,7 +1453,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -1458,7 +1473,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -1478,7 +1493,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -1498,7 +1513,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -1518,7 +1533,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -1542,7 +1557,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -1562,7 +1577,7 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -1582,7 +1597,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -1602,7 +1617,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -1624,7 +1639,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -1644,7 +1659,7 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -1664,7 +1679,7 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -1684,7 +1699,7 @@
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>30</v>
       </c>
@@ -1704,7 +1719,7 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -1724,7 +1739,7 @@
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>32</v>
       </c>
@@ -1748,7 +1763,7 @@
       </c>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>33</v>
       </c>
@@ -1774,7 +1789,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>34</v>
       </c>
@@ -1798,7 +1813,7 @@
       </c>
       <c r="H36" s="3"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>35</v>
       </c>
@@ -1814,7 +1829,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>36</v>
       </c>
@@ -1834,7 +1849,7 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>37</v>
       </c>
@@ -1854,7 +1869,7 @@
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>38</v>
       </c>
@@ -1874,7 +1889,7 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>39</v>
       </c>
@@ -1894,7 +1909,7 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>40</v>
       </c>
@@ -1914,7 +1929,7 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>41</v>
       </c>
@@ -1928,7 +1943,7 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>42</v>
       </c>
@@ -1944,77 +1959,107 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>43</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
+      <c r="C45" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>44</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
+      <c r="C46" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>45</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
+      <c r="C47" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>46</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
+      <c r="C48" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>47</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
+      <c r="C49" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>48</v>
       </c>
@@ -2026,7 +2071,7 @@
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>49</v>
       </c>
@@ -2038,7 +2083,7 @@
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>50</v>
       </c>

--- a/Reading&Movie/Felix Du的图书馆索引.xlsx
+++ b/Reading&Movie/Felix Du的图书馆索引.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Reading&amp;Movie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E631E8-CDBD-4689-B75E-F1A053985E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46EDC36-A7C2-4A61-9F85-4FCCD3747163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="185">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -666,6 +666,102 @@
   </si>
   <si>
     <t>人物研究</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《心海的消息》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人民文学出版社（2016）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>演讲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《装脏》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林树京</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作家出版社（2024.11）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中篇小说</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作者亲签</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《查令十字街84号》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海莲.汉芙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>译林出版社（2016.4）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>书信集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你们若恰好路经查令十字街84号，请代我献上一吻，我亏欠她良多…...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《三体：死神永生》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《一地鸡毛》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘震云</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长江文艺出版社（2011.09）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小说集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>历史/人际关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>都是十五六岁睡打麦场的孩子，怎么一出社会就变得如此虚伪。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《毛泽东诗词全集赏读》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>麓山子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>太白文艺出版社（2007.9）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诗词赏析</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -673,7 +769,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -694,6 +793,13 @@
       <name val="黑体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -740,10 +846,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -757,9 +866,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1037,21 +1156,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H82"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" style="1" customWidth="1"/>
     <col min="3" max="3" width="21" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="41.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="33.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="41.109375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -1063,7 +1182,7 @@
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1082,14 +1201,14 @@
       <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="5" t="s">
         <v>126</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1108,10 +1227,10 @@
       <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="6"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1130,10 +1249,10 @@
       <c r="F4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="3"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1152,10 +1271,10 @@
       <c r="F5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="3"/>
+      <c r="G5" s="6"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1174,12 +1293,12 @@
       <c r="F6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="3"/>
+      <c r="G6" s="6"/>
       <c r="H6" s="3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1198,12 +1317,12 @@
       <c r="F7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="3"/>
+      <c r="G7" s="6"/>
       <c r="H7" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1222,10 +1341,10 @@
       <c r="F8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="3"/>
+      <c r="G8" s="6"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1242,10 +1361,10 @@
         <v>38</v>
       </c>
       <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="G9" s="6"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1264,10 +1383,10 @@
       <c r="F10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="3"/>
+      <c r="G10" s="6"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1284,10 +1403,10 @@
         <v>47</v>
       </c>
       <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="G11" s="6"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1306,10 +1425,10 @@
       <c r="F12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="3"/>
+      <c r="G12" s="6"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1326,10 +1445,10 @@
         <v>33</v>
       </c>
       <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="G13" s="6"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1346,10 +1465,10 @@
         <v>38</v>
       </c>
       <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="G14" s="6"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1368,10 +1487,10 @@
       <c r="F15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="3"/>
+      <c r="G15" s="6"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1390,10 +1509,10 @@
       <c r="F16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="3"/>
+      <c r="G16" s="6"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1410,10 +1529,10 @@
         <v>63</v>
       </c>
       <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="G17" s="6"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1430,10 +1549,10 @@
         <v>10</v>
       </c>
       <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+      <c r="G18" s="6"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -1450,10 +1569,10 @@
         <v>70</v>
       </c>
       <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="G19" s="6"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -1470,10 +1589,10 @@
         <v>10</v>
       </c>
       <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="G20" s="6"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -1490,10 +1609,10 @@
         <v>10</v>
       </c>
       <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+      <c r="G21" s="6"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -1510,10 +1629,10 @@
         <v>80</v>
       </c>
       <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
+      <c r="G22" s="6"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -1530,10 +1649,10 @@
         <v>10</v>
       </c>
       <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="G23" s="6"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -1552,12 +1671,12 @@
       <c r="F24" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G24" s="3"/>
+      <c r="G24" s="6"/>
       <c r="H24" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -1574,10 +1693,10 @@
         <v>98</v>
       </c>
       <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
+      <c r="G25" s="6"/>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -1594,10 +1713,10 @@
         <v>80</v>
       </c>
       <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
+      <c r="G26" s="6"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -1614,10 +1733,10 @@
         <v>95</v>
       </c>
       <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
+      <c r="G27" s="6"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -1634,12 +1753,12 @@
         <v>99</v>
       </c>
       <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
+      <c r="G28" s="6"/>
       <c r="H28" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -1656,10 +1775,10 @@
         <v>106</v>
       </c>
       <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
+      <c r="G29" s="6"/>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -1676,10 +1795,10 @@
         <v>10</v>
       </c>
       <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+      <c r="G30" s="6"/>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -1696,10 +1815,10 @@
         <v>38</v>
       </c>
       <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+      <c r="G31" s="6"/>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>30</v>
       </c>
@@ -1716,10 +1835,10 @@
         <v>114</v>
       </c>
       <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+      <c r="G32" s="6"/>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -1736,10 +1855,10 @@
         <v>118</v>
       </c>
       <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
+      <c r="G33" s="6"/>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>32</v>
       </c>
@@ -1758,12 +1877,12 @@
       <c r="F34" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="6" t="s">
         <v>127</v>
       </c>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>33</v>
       </c>
@@ -1782,14 +1901,14 @@
       <c r="F35" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="6" t="s">
         <v>128</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>34</v>
       </c>
@@ -1808,12 +1927,12 @@
       <c r="F36" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="6" t="s">
         <v>131</v>
       </c>
       <c r="H36" s="3"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>35</v>
       </c>
@@ -1824,12 +1943,12 @@
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
+      <c r="G37" s="6"/>
       <c r="H37" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>36</v>
       </c>
@@ -1846,10 +1965,10 @@
         <v>148</v>
       </c>
       <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
+      <c r="G38" s="6"/>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>37</v>
       </c>
@@ -1866,10 +1985,10 @@
         <v>148</v>
       </c>
       <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
+      <c r="G39" s="6"/>
       <c r="H39" s="3"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>38</v>
       </c>
@@ -1886,10 +2005,10 @@
         <v>148</v>
       </c>
       <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
+      <c r="G40" s="6"/>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>39</v>
       </c>
@@ -1906,10 +2025,10 @@
         <v>148</v>
       </c>
       <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
+      <c r="G41" s="6"/>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>40</v>
       </c>
@@ -1926,10 +2045,10 @@
         <v>19</v>
       </c>
       <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
+      <c r="G42" s="6"/>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>41</v>
       </c>
@@ -1940,10 +2059,10 @@
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
+      <c r="G43" s="6"/>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>42</v>
       </c>
@@ -1956,10 +2075,10 @@
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
+      <c r="G44" s="6"/>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>43</v>
       </c>
@@ -1976,10 +2095,10 @@
         <v>160</v>
       </c>
       <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
+      <c r="G45" s="6"/>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>44</v>
       </c>
@@ -1996,10 +2115,10 @@
         <v>160</v>
       </c>
       <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
+      <c r="G46" s="6"/>
       <c r="H46" s="3"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>45</v>
       </c>
@@ -2016,10 +2135,10 @@
         <v>160</v>
       </c>
       <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
+      <c r="G47" s="6"/>
       <c r="H47" s="3"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>46</v>
       </c>
@@ -2036,10 +2155,10 @@
         <v>160</v>
       </c>
       <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
+      <c r="G48" s="6"/>
       <c r="H48" s="3"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>47</v>
       </c>
@@ -2056,44 +2175,458 @@
         <v>160</v>
       </c>
       <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
+      <c r="G49" s="6"/>
       <c r="H49" s="3"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>48</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
+      <c r="B50" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>163</v>
+      </c>
       <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
+      <c r="G50" s="6"/>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>49</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
+      <c r="B51" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G51" s="6"/>
+      <c r="H51" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>50</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
+      <c r="B52" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
+      <c r="G52" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <v>51</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
+        <v>52</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="H54" s="3"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
+        <v>53</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="3"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>54</v>
+      </c>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <v>55</v>
+      </c>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
+        <v>56</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="3"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
+        <v>57</v>
+      </c>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
+        <v>58</v>
+      </c>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="3"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
+        <v>59</v>
+      </c>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="3"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
+        <v>60</v>
+      </c>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="3"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
+        <v>61</v>
+      </c>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="3"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
+        <v>62</v>
+      </c>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="3"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
+        <v>63</v>
+      </c>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="3"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
+        <v>64</v>
+      </c>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="3"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
+        <v>65</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="3"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
+        <v>66</v>
+      </c>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="3"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
+        <v>67</v>
+      </c>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="3"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
+        <v>68</v>
+      </c>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="3"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
+        <v>69</v>
+      </c>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="3"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
+        <v>70</v>
+      </c>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="3"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
+        <v>71</v>
+      </c>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="3"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
+        <v>72</v>
+      </c>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="3"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
+        <v>73</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="3"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
+        <v>74</v>
+      </c>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="3"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
+        <v>75</v>
+      </c>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="3"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
+        <v>76</v>
+      </c>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="3"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
+        <v>77</v>
+      </c>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="3"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
+        <v>78</v>
+      </c>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="3"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
+        <v>79</v>
+      </c>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="3"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
+        <v>80</v>
+      </c>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Reading&Movie/Felix Du的图书馆索引.xlsx
+++ b/Reading&Movie/Felix Du的图书馆索引.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Reading&amp;Movie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46EDC36-A7C2-4A61-9F85-4FCCD3747163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817B8998-C744-4727-8FB7-ED5D758D4260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="193">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -762,6 +762,38 @@
   </si>
   <si>
     <t>诗词赏析</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《云边有个小卖部》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张嘉佳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖南文艺出版社（2018.7）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亲情/爱情/治愈/励志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《生命是什么》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>埃尔温.薛定谔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海南出版社（2017.1）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命科学/研究</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -863,9 +895,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -874,6 +903,9 @@
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1165,22 +1197,22 @@
     <col min="4" max="4" width="33.21875" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="41.109375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="41.109375" style="6" customWidth="1"/>
     <col min="8" max="8" width="17.44140625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1201,7 +1233,7 @@
       <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>126</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -1227,7 +1259,7 @@
       <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="6"/>
+      <c r="G3" s="5"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1249,7 +1281,7 @@
       <c r="F4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="6"/>
+      <c r="G4" s="5"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1271,7 +1303,7 @@
       <c r="F5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="6"/>
+      <c r="G5" s="5"/>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1293,7 +1325,7 @@
       <c r="F6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="6"/>
+      <c r="G6" s="5"/>
       <c r="H6" s="3" t="s">
         <v>132</v>
       </c>
@@ -1317,7 +1349,7 @@
       <c r="F7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="6"/>
+      <c r="G7" s="5"/>
       <c r="H7" s="3" t="s">
         <v>101</v>
       </c>
@@ -1341,7 +1373,7 @@
       <c r="F8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="6"/>
+      <c r="G8" s="5"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1361,7 +1393,7 @@
         <v>38</v>
       </c>
       <c r="F9" s="3"/>
-      <c r="G9" s="6"/>
+      <c r="G9" s="5"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1383,7 +1415,7 @@
       <c r="F10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="6"/>
+      <c r="G10" s="5"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1403,7 +1435,7 @@
         <v>47</v>
       </c>
       <c r="F11" s="3"/>
-      <c r="G11" s="6"/>
+      <c r="G11" s="5"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1425,7 +1457,7 @@
       <c r="F12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="6"/>
+      <c r="G12" s="5"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,7 +1477,7 @@
         <v>33</v>
       </c>
       <c r="F13" s="3"/>
-      <c r="G13" s="6"/>
+      <c r="G13" s="5"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1465,7 +1497,7 @@
         <v>38</v>
       </c>
       <c r="F14" s="3"/>
-      <c r="G14" s="6"/>
+      <c r="G14" s="5"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1487,7 +1519,7 @@
       <c r="F15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="6"/>
+      <c r="G15" s="5"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1509,7 +1541,7 @@
       <c r="F16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="6"/>
+      <c r="G16" s="5"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1529,7 +1561,7 @@
         <v>63</v>
       </c>
       <c r="F17" s="3"/>
-      <c r="G17" s="6"/>
+      <c r="G17" s="5"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1549,7 +1581,7 @@
         <v>10</v>
       </c>
       <c r="F18" s="3"/>
-      <c r="G18" s="6"/>
+      <c r="G18" s="5"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1569,7 +1601,7 @@
         <v>70</v>
       </c>
       <c r="F19" s="3"/>
-      <c r="G19" s="6"/>
+      <c r="G19" s="5"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1589,7 +1621,7 @@
         <v>10</v>
       </c>
       <c r="F20" s="3"/>
-      <c r="G20" s="6"/>
+      <c r="G20" s="5"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1609,7 +1641,7 @@
         <v>10</v>
       </c>
       <c r="F21" s="3"/>
-      <c r="G21" s="6"/>
+      <c r="G21" s="5"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1629,7 +1661,7 @@
         <v>80</v>
       </c>
       <c r="F22" s="3"/>
-      <c r="G22" s="6"/>
+      <c r="G22" s="5"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1649,7 +1681,7 @@
         <v>10</v>
       </c>
       <c r="F23" s="3"/>
-      <c r="G23" s="6"/>
+      <c r="G23" s="5"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1671,7 +1703,7 @@
       <c r="F24" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G24" s="6"/>
+      <c r="G24" s="5"/>
       <c r="H24" s="3" t="s">
         <v>142</v>
       </c>
@@ -1693,7 +1725,7 @@
         <v>98</v>
       </c>
       <c r="F25" s="3"/>
-      <c r="G25" s="6"/>
+      <c r="G25" s="5"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1713,7 +1745,7 @@
         <v>80</v>
       </c>
       <c r="F26" s="3"/>
-      <c r="G26" s="6"/>
+      <c r="G26" s="5"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1733,7 +1765,7 @@
         <v>95</v>
       </c>
       <c r="F27" s="3"/>
-      <c r="G27" s="6"/>
+      <c r="G27" s="5"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1753,7 +1785,7 @@
         <v>99</v>
       </c>
       <c r="F28" s="3"/>
-      <c r="G28" s="6"/>
+      <c r="G28" s="5"/>
       <c r="H28" s="3" t="s">
         <v>101</v>
       </c>
@@ -1775,7 +1807,7 @@
         <v>106</v>
       </c>
       <c r="F29" s="3"/>
-      <c r="G29" s="6"/>
+      <c r="G29" s="5"/>
       <c r="H29" s="3"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1795,7 +1827,7 @@
         <v>10</v>
       </c>
       <c r="F30" s="3"/>
-      <c r="G30" s="6"/>
+      <c r="G30" s="5"/>
       <c r="H30" s="3"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1815,7 +1847,7 @@
         <v>38</v>
       </c>
       <c r="F31" s="3"/>
-      <c r="G31" s="6"/>
+      <c r="G31" s="5"/>
       <c r="H31" s="3"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1835,7 +1867,7 @@
         <v>114</v>
       </c>
       <c r="F32" s="3"/>
-      <c r="G32" s="6"/>
+      <c r="G32" s="5"/>
       <c r="H32" s="3"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1855,7 +1887,7 @@
         <v>118</v>
       </c>
       <c r="F33" s="3"/>
-      <c r="G33" s="6"/>
+      <c r="G33" s="5"/>
       <c r="H33" s="3"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1877,7 +1909,7 @@
       <c r="F34" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="5" t="s">
         <v>127</v>
       </c>
       <c r="H34" s="3"/>
@@ -1901,7 +1933,7 @@
       <c r="F35" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="5" t="s">
         <v>128</v>
       </c>
       <c r="H35" s="3" t="s">
@@ -1927,7 +1959,7 @@
       <c r="F36" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="5" t="s">
         <v>131</v>
       </c>
       <c r="H36" s="3"/>
@@ -1943,7 +1975,7 @@
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
-      <c r="G37" s="6"/>
+      <c r="G37" s="5"/>
       <c r="H37" s="3" t="s">
         <v>143</v>
       </c>
@@ -1965,7 +1997,7 @@
         <v>148</v>
       </c>
       <c r="F38" s="3"/>
-      <c r="G38" s="6"/>
+      <c r="G38" s="5"/>
       <c r="H38" s="3"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -1985,7 +2017,7 @@
         <v>148</v>
       </c>
       <c r="F39" s="3"/>
-      <c r="G39" s="6"/>
+      <c r="G39" s="5"/>
       <c r="H39" s="3"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -2005,7 +2037,7 @@
         <v>148</v>
       </c>
       <c r="F40" s="3"/>
-      <c r="G40" s="6"/>
+      <c r="G40" s="5"/>
       <c r="H40" s="3"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -2025,7 +2057,7 @@
         <v>148</v>
       </c>
       <c r="F41" s="3"/>
-      <c r="G41" s="6"/>
+      <c r="G41" s="5"/>
       <c r="H41" s="3"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -2045,7 +2077,7 @@
         <v>19</v>
       </c>
       <c r="F42" s="3"/>
-      <c r="G42" s="6"/>
+      <c r="G42" s="5"/>
       <c r="H42" s="3"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -2059,7 +2091,7 @@
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
-      <c r="G43" s="6"/>
+      <c r="G43" s="5"/>
       <c r="H43" s="3"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -2075,7 +2107,7 @@
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
-      <c r="G44" s="6"/>
+      <c r="G44" s="5"/>
       <c r="H44" s="3"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -2095,7 +2127,7 @@
         <v>160</v>
       </c>
       <c r="F45" s="3"/>
-      <c r="G45" s="6"/>
+      <c r="G45" s="5"/>
       <c r="H45" s="3"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -2115,7 +2147,7 @@
         <v>160</v>
       </c>
       <c r="F46" s="3"/>
-      <c r="G46" s="6"/>
+      <c r="G46" s="5"/>
       <c r="H46" s="3"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -2135,7 +2167,7 @@
         <v>160</v>
       </c>
       <c r="F47" s="3"/>
-      <c r="G47" s="6"/>
+      <c r="G47" s="5"/>
       <c r="H47" s="3"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -2155,7 +2187,7 @@
         <v>160</v>
       </c>
       <c r="F48" s="3"/>
-      <c r="G48" s="6"/>
+      <c r="G48" s="5"/>
       <c r="H48" s="3"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -2175,7 +2207,7 @@
         <v>160</v>
       </c>
       <c r="F49" s="3"/>
-      <c r="G49" s="6"/>
+      <c r="G49" s="5"/>
       <c r="H49" s="3"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -2195,7 +2227,7 @@
         <v>163</v>
       </c>
       <c r="F50" s="3"/>
-      <c r="G50" s="6"/>
+      <c r="G50" s="5"/>
       <c r="H50" s="3"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -2215,7 +2247,7 @@
         <v>167</v>
       </c>
       <c r="F51" s="3"/>
-      <c r="G51" s="6"/>
+      <c r="G51" s="5"/>
       <c r="H51" s="3" t="s">
         <v>168</v>
       </c>
@@ -2237,7 +2269,7 @@
         <v>172</v>
       </c>
       <c r="F52" s="3"/>
-      <c r="G52" s="6" t="s">
+      <c r="G52" s="5" t="s">
         <v>173</v>
       </c>
       <c r="H52" s="3" t="s">
@@ -2257,7 +2289,7 @@
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
-      <c r="G53" s="6"/>
+      <c r="G53" s="5"/>
       <c r="H53" s="3"/>
     </row>
     <row r="54" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
@@ -2279,7 +2311,7 @@
       <c r="F54" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G54" s="6" t="s">
+      <c r="G54" s="5" t="s">
         <v>180</v>
       </c>
       <c r="H54" s="3"/>
@@ -2301,31 +2333,49 @@
         <v>184</v>
       </c>
       <c r="F55" s="3"/>
-      <c r="G55" s="6"/>
+      <c r="G55" s="5"/>
       <c r="H55" s="3"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>54</v>
       </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="6"/>
+      <c r="B56" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G56" s="5"/>
       <c r="H56" s="3"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>55</v>
       </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
+      <c r="B57" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="F57" s="3"/>
-      <c r="G57" s="6"/>
+      <c r="G57" s="5"/>
       <c r="H57" s="3"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -2337,7 +2387,7 @@
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="6"/>
+      <c r="G58" s="5"/>
       <c r="H58" s="3"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -2349,7 +2399,7 @@
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
-      <c r="G59" s="6"/>
+      <c r="G59" s="5"/>
       <c r="H59" s="3"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -2361,7 +2411,7 @@
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
-      <c r="G60" s="6"/>
+      <c r="G60" s="5"/>
       <c r="H60" s="3"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -2373,7 +2423,7 @@
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
-      <c r="G61" s="6"/>
+      <c r="G61" s="5"/>
       <c r="H61" s="3"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -2385,7 +2435,7 @@
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
-      <c r="G62" s="6"/>
+      <c r="G62" s="5"/>
       <c r="H62" s="3"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -2397,7 +2447,7 @@
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
-      <c r="G63" s="6"/>
+      <c r="G63" s="5"/>
       <c r="H63" s="3"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -2409,7 +2459,7 @@
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
-      <c r="G64" s="6"/>
+      <c r="G64" s="5"/>
       <c r="H64" s="3"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -2421,7 +2471,7 @@
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
-      <c r="G65" s="6"/>
+      <c r="G65" s="5"/>
       <c r="H65" s="3"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -2433,7 +2483,7 @@
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
-      <c r="G66" s="6"/>
+      <c r="G66" s="5"/>
       <c r="H66" s="3"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -2445,7 +2495,7 @@
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
-      <c r="G67" s="6"/>
+      <c r="G67" s="5"/>
       <c r="H67" s="3"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -2457,7 +2507,7 @@
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
-      <c r="G68" s="6"/>
+      <c r="G68" s="5"/>
       <c r="H68" s="3"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -2469,7 +2519,7 @@
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
-      <c r="G69" s="6"/>
+      <c r="G69" s="5"/>
       <c r="H69" s="3"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -2481,7 +2531,7 @@
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
-      <c r="G70" s="6"/>
+      <c r="G70" s="5"/>
       <c r="H70" s="3"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -2493,7 +2543,7 @@
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
-      <c r="G71" s="6"/>
+      <c r="G71" s="5"/>
       <c r="H71" s="3"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -2505,7 +2555,7 @@
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
-      <c r="G72" s="6"/>
+      <c r="G72" s="5"/>
       <c r="H72" s="3"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -2517,7 +2567,7 @@
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
-      <c r="G73" s="6"/>
+      <c r="G73" s="5"/>
       <c r="H73" s="3"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -2529,7 +2579,7 @@
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
-      <c r="G74" s="6"/>
+      <c r="G74" s="5"/>
       <c r="H74" s="3"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -2541,7 +2591,7 @@
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
-      <c r="G75" s="6"/>
+      <c r="G75" s="5"/>
       <c r="H75" s="3"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -2553,7 +2603,7 @@
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
-      <c r="G76" s="6"/>
+      <c r="G76" s="5"/>
       <c r="H76" s="3"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -2565,7 +2615,7 @@
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
-      <c r="G77" s="6"/>
+      <c r="G77" s="5"/>
       <c r="H77" s="3"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -2577,7 +2627,7 @@
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
-      <c r="G78" s="6"/>
+      <c r="G78" s="5"/>
       <c r="H78" s="3"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -2589,7 +2639,7 @@
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
-      <c r="G79" s="6"/>
+      <c r="G79" s="5"/>
       <c r="H79" s="3"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -2601,7 +2651,7 @@
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
-      <c r="G80" s="6"/>
+      <c r="G80" s="5"/>
       <c r="H80" s="3"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -2613,7 +2663,7 @@
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
-      <c r="G81" s="6"/>
+      <c r="G81" s="5"/>
       <c r="H81" s="3"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -2625,7 +2675,7 @@
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
-      <c r="G82" s="6"/>
+      <c r="G82" s="5"/>
       <c r="H82" s="3"/>
     </row>
   </sheetData>

--- a/Reading&Movie/Felix Du的图书馆索引.xlsx
+++ b/Reading&Movie/Felix Du的图书馆索引.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Reading&amp;Movie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817B8998-C744-4727-8FB7-ED5D758D4260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041EF4C2-BAC0-4833-AAD0-B0D0B8DEA649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="196">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -794,6 +794,18 @@
   </si>
   <si>
     <t>生命科学/研究</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛姆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>民主与建设出版社（2017.3）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长篇小说/英国</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2382,10 +2394,18 @@
       <c r="A58" s="3">
         <v>56</v>
       </c>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
+      <c r="B58" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="F58" s="3"/>
       <c r="G58" s="5"/>
       <c r="H58" s="3"/>

--- a/Reading&Movie/Felix Du的图书馆索引.xlsx
+++ b/Reading&Movie/Felix Du的图书馆索引.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Reading&amp;Movie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041EF4C2-BAC0-4833-AAD0-B0D0B8DEA649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1070D0-6050-4CA6-BE89-2C646AF509A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="200">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -806,6 +806,22 @@
   </si>
   <si>
     <t>长篇小说/英国</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《明史讲义》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孟森</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏人民出版社（2019.3）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国历史/研究/明代</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2414,10 +2430,18 @@
       <c r="A59" s="3">
         <v>57</v>
       </c>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
+      <c r="B59" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>199</v>
+      </c>
       <c r="F59" s="3"/>
       <c r="G59" s="5"/>
       <c r="H59" s="3"/>

--- a/Reading&Movie/Felix Du的图书馆索引.xlsx
+++ b/Reading&Movie/Felix Du的图书馆索引.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Reading&amp;Movie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1070D0-6050-4CA6-BE89-2C646AF509A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E87C2C-53BA-4993-BC4D-B4EAAFE31FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4344" yWindow="204" windowWidth="16896" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="204">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -822,6 +822,22 @@
   </si>
   <si>
     <t>中国历史/研究/明代</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《生怕多情》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诸荣会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>百花文艺出版社（2011.5）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>历史/散文集</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2450,10 +2466,18 @@
       <c r="A60" s="3">
         <v>58</v>
       </c>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
+      <c r="B60" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="F60" s="3"/>
       <c r="G60" s="5"/>
       <c r="H60" s="3"/>

--- a/Reading&Movie/Felix Du的图书馆索引.xlsx
+++ b/Reading&Movie/Felix Du的图书馆索引.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Reading&amp;Movie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E87C2C-53BA-4993-BC4D-B4EAAFE31FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA47B96-5E6E-47CA-9FAE-1086CC004428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4344" yWindow="204" windowWidth="16896" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="215">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -838,6 +838,49 @@
   </si>
   <si>
     <t>历史/散文集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《千只鹤》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>川端康成</t>
+  </si>
+  <si>
+    <t>诗云书社救助盲盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《名人传》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗曼.罗兰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《风义的怀思》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈建华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《论无边的现实主义》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗杰.加洛蒂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《空楼梯》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡弦</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1242,7 +1285,7 @@
     <col min="5" max="5" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.44140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="41.109375" style="6" customWidth="1"/>
-    <col min="8" max="8" width="17.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2486,61 +2529,91 @@
       <c r="A61" s="3">
         <v>59</v>
       </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
+      <c r="B61" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="5"/>
-      <c r="H61" s="3"/>
+      <c r="H61" s="3" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>60</v>
       </c>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
+      <c r="B62" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="5"/>
-      <c r="H62" s="3"/>
+      <c r="H62" s="3" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>61</v>
       </c>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
+      <c r="B63" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="5"/>
-      <c r="H63" s="3"/>
+      <c r="H63" s="3" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>62</v>
       </c>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
+      <c r="B64" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="5"/>
-      <c r="H64" s="3"/>
+      <c r="H64" s="3" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>63</v>
       </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
+      <c r="B65" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="5"/>
-      <c r="H65" s="3"/>
+      <c r="H65" s="3" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
